--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/avg/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct+DICE/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -1021,6 +1021,154 @@
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>dice_p=10,ash_p=None,react_th=1.0,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>97.73</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=1.0,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=1.0,scale_th=0.1,type=avg</t>
         </is>
       </c>
     </row>
